--- a/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,41; 81,69</t>
+          <t>20,15; 87,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,7; 100,0</t>
+          <t>20,45; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,78; 72,08</t>
+          <t>22,35; 75,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,28; 89,83</t>
+          <t>26,82; 89,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,47</t>
+          <t>7,81; 64,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 70,83</t>
+          <t>18,46; 70,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,54; 80,47</t>
+          <t>36,33; 80,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,81; 69,3</t>
+          <t>19,67; 69,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,89; 63,6</t>
+          <t>24,56; 61,65</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,79; 80,97</t>
+          <t>31,33; 81,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,17; 68,77</t>
+          <t>22,21; 68,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,4; 100,0</t>
+          <t>51,8; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 76,9</t>
+          <t>11,4; 77,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,42; 83,15</t>
+          <t>41,54; 81,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,37; 75,99</t>
+          <t>25,36; 76,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,21; 72,07</t>
+          <t>31,44; 69,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,5; 70,65</t>
+          <t>39,42; 71,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,55; 82,85</t>
+          <t>48,37; 84,32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>23,67; 100,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17,98; 81,21</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19,89; 100,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,09; 81,1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>21,26; 80,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>55,59; 100</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>20,13; 100,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,88; 86,4</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,91; 100,0</t>
+          <t>41,52; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,13; 75,19</t>
+          <t>31,45; 76,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 100,0</t>
+          <t>21,16; 100,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,76</t>
+          <t>0,0; 63,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 71,74</t>
+          <t>16,91; 71,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 61,41</t>
+          <t>11,34; 61,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 75,78</t>
+          <t>16,84; 69,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 79,42</t>
+          <t>11,06; 80,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 76,11</t>
+          <t>19,82; 75,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,17; 58,94</t>
+          <t>14,86; 54,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,43; 64,93</t>
+          <t>22,64; 69,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,63; 59,99</t>
+          <t>21,83; 59,01</t>
         </is>
       </c>
     </row>
@@ -1117,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,5; 100,0</t>
+          <t>47,54; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,35</t>
+          <t>0,0; 76,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 79,49</t>
+          <t>11,0; 79,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,24 +1148,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,7; 86,37</t>
+          <t>41,95; 82,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 66,38</t>
+          <t>9,44; 72,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,27 +1228,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,24; 100,0</t>
+          <t>20,29; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,31</t>
+          <t>0,0; 61,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,0; 100,0</t>
+          <t>18,89; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,19</t>
+          <t>0,0; 70,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1257,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,68; 90,63</t>
+          <t>30,38; 90,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 58,41</t>
+          <t>13,64; 62,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1274,7 +1275,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45,12; 100,0</t>
+          <t>44,7; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,52; 78,26</t>
+          <t>18,93; 80,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,81; 78,43</t>
+          <t>11,28; 79,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,37</t>
+          <t>0,0; 65,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,76; 89,4</t>
+          <t>17,32; 89,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,92; 87,59</t>
+          <t>15,23; 87,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,44; 81,71</t>
+          <t>34,57; 81,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>28,83; 74,9</t>
+          <t>26,6; 73,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 76,69</t>
+          <t>26,39; 74,95</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,14; 71,48</t>
+          <t>10,0; 65,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,82; 64,85</t>
+          <t>9,2; 64,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,71; 57,96</t>
+          <t>14,37; 53,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,38; 55,14</t>
+          <t>14,79; 54,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,17; 66,31</t>
+          <t>17,93; 66,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,39; 62,39</t>
+          <t>14,55; 60,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 50,69</t>
+          <t>15,55; 48,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,95; 56,8</t>
+          <t>21,61; 57,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 50,27</t>
+          <t>20,51; 50,56</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>43,51; 67,85</t>
+          <t>44,01; 68,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,82; 62,53</t>
+          <t>41,34; 61,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,69; 57,21</t>
+          <t>36,39; 58,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35,85; 58,92</t>
+          <t>34,77; 57,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,07; 58,52</t>
+          <t>36,72; 57,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,32; 57,36</t>
+          <t>33,47; 57,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,54; 58,98</t>
+          <t>42,59; 59,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41,96; 56,64</t>
+          <t>41,8; 56,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,2; 53,8</t>
+          <t>38,53; 53,84</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4117</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8128</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5742</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8397</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1154; 5010</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1011; 4945</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2049; 6930</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2116; 7083</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>642; 5276</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1871; 7169</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4949; 10976</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2591; 9105</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4741; 11900</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5538</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8451</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14473</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11713</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3229; 8392</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2696; 8267</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4773; 9215</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>663; 4512</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5777; 11398</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2031; 6113</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5071; 11221</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10265; 18557</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>8330; 14521</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4209</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>715; 3022</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1442; 6515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>624; 3138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1462; 5904</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1355</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2558; 6160</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4813; 11688</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>741; 3504</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3812</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4720</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5125</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>7802</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4126</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1444; 6089</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1116; 6032</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1376; 5669</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>703; 5136</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1919; 7309</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2173; 7992</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3371; 10359</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4261; 11521</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7021</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9918</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3989; 8390</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3438</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>700; 5041</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6192; 12173</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>594; 4549</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2295</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2996</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>743; 3662</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3207</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>582; 3082</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3544</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 1766</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2049; 6101</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1399; 6395</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2495</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6822</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6869</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3385; 7572</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1355; 5760</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>672; 4721</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2644</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1046; 5378</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>738; 4246</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4015; 9522</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3510; 9744</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2849; 8093</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4351</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3971</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>8044</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>580; 3788</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>633; 4439</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1949; 7224</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2055; 7561</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1856; 6859</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1496; 6260</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3064; 9624</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3723; 9917</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4889; 12055</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>24550</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>31407</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>25548</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>46267</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>47354</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>19310; 29995</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>25338; 37976</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>20062; 32430</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>16241; 26946</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>23341; 36335</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>16019; 27576</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>38578; 53788</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>52194; 70015</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>39679; 55447</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,15; 87,48</t>
+          <t>21,7; 88,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,45; 100,0</t>
+          <t>25,37; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 75,6</t>
+          <t>19,91; 74,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,82; 89,75</t>
+          <t>28,55; 91,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 64,13</t>
+          <t>8,24; 63,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 70,73</t>
+          <t>15,39; 70,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,33; 80,59</t>
+          <t>35,72; 80,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,67; 69,12</t>
+          <t>22,28; 68,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,56; 61,65</t>
+          <t>24,35; 62,72</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,33; 81,41</t>
+          <t>29,71; 77,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,21; 68,11</t>
+          <t>23,31; 69,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,8; 100,0</t>
+          <t>51,62; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,4; 77,52</t>
+          <t>11,35; 77,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,54; 81,96</t>
+          <t>43,23; 82,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,36; 76,34</t>
+          <t>25,44; 76,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,44; 69,57</t>
+          <t>33,03; 71,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,42; 71,26</t>
+          <t>39,96; 70,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,37; 84,32</t>
+          <t>48,51; 84,54</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,98; 81,21</t>
+          <t>25,45; 80,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 81,1</t>
+          <t>26,74; 86,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,52; 100,0</t>
+          <t>42,02; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31,45; 76,38</t>
+          <t>32,27; 75,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,96</t>
+          <t>0,0; 59,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 71,32</t>
+          <t>19,1; 72,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 61,29</t>
+          <t>11,09; 61,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 69,37</t>
+          <t>17,14; 74,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 80,85</t>
+          <t>10,58; 78,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 75,5</t>
+          <t>19,33; 73,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 54,65</t>
+          <t>16,47; 57,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,64; 69,58</t>
+          <t>21,85; 66,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,83; 59,01</t>
+          <t>23,21; 61,99</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>47,54; 100,0</t>
+          <t>56,3; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,22</t>
+          <t>0,0; 76,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,0; 79,15</t>
+          <t>11,38; 80,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,95; 82,48</t>
+          <t>42,52; 85,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 72,27</t>
+          <t>9,45; 68,44</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,4</t>
+          <t>0,0; 73,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,39</t>
+          <t>0,0; 71,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 90,46</t>
+          <t>35,74; 90,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 62,35</t>
+          <t>7,25; 58,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,7; 100,0</t>
+          <t>53,43; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,93; 80,47</t>
+          <t>19,01; 80,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,28; 79,34</t>
+          <t>13,22; 78,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,32; 89,04</t>
+          <t>18,03; 89,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,23; 87,59</t>
+          <t>14,59; 87,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,57; 81,98</t>
+          <t>35,23; 82,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,6; 73,83</t>
+          <t>29,06; 76,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,39; 74,95</t>
+          <t>27,59; 77,23</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 65,27</t>
+          <t>10,28; 69,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 64,51</t>
+          <t>9,67; 70,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,37; 53,27</t>
+          <t>13,03; 54,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,79; 54,42</t>
+          <t>13,15; 51,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,93; 66,26</t>
+          <t>16,67; 64,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,55; 60,9</t>
+          <t>16,53; 61,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,55; 48,86</t>
+          <t>16,37; 49,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,61; 57,54</t>
+          <t>20,6; 57,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 50,56</t>
+          <t>19,61; 50,83</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44,01; 68,36</t>
+          <t>44,04; 68,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,34; 61,96</t>
+          <t>41,12; 62,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,39; 58,83</t>
+          <t>36,33; 56,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,77; 57,69</t>
+          <t>33,93; 58,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,72; 57,17</t>
+          <t>36,04; 57,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,47; 57,62</t>
+          <t>33,87; 57,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,59; 59,38</t>
+          <t>43,1; 60,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41,8; 56,08</t>
+          <t>42,14; 56,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,53; 53,84</t>
+          <t>37,95; 53,78</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1154; 5010</t>
+          <t>1243; 5071</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1011; 4945</t>
+          <t>1254; 4945</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2049; 6930</t>
+          <t>1826; 6808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2116; 7083</t>
+          <t>2253; 7190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>642; 5276</t>
+          <t>678; 5262</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1871; 7169</t>
+          <t>1560; 7133</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4949; 10976</t>
+          <t>4865; 10901</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2591; 9105</t>
+          <t>2935; 9027</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4741; 11900</t>
+          <t>4700; 12107</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3229; 8392</t>
+          <t>3062; 7989</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2696; 8267</t>
+          <t>2830; 8458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4773; 9215</t>
+          <t>4756; 9215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>663; 4512</t>
+          <t>661; 4514</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5777; 11398</t>
+          <t>6011; 11482</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2031; 6113</t>
+          <t>2037; 6134</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5071; 11221</t>
+          <t>5327; 11479</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10265; 18557</t>
+          <t>10406; 18319</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8330; 14521</t>
+          <t>8354; 14560</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1442; 6515</t>
+          <t>2042; 6494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1462; 5904</t>
+          <t>1946; 6310</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2558; 6160</t>
+          <t>2588; 6160</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4813; 11688</t>
+          <t>4939; 11565</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4126</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1444; 6089</t>
+          <t>1631; 6169</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1116; 6032</t>
+          <t>1091; 6022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1376; 5669</t>
+          <t>1401; 6101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>703; 5136</t>
+          <t>672; 5015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1919; 7309</t>
+          <t>1872; 7135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2173; 7992</t>
+          <t>2409; 8355</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3371; 10359</t>
+          <t>3253; 9896</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4261; 11521</t>
+          <t>4532; 12103</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3989; 8390</t>
+          <t>4723; 8390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>700; 5041</t>
+          <t>724; 5103</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6192; 12173</t>
+          <t>6276; 12626</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>594; 4549</t>
+          <t>595; 4308</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3207</t>
+          <t>0; 3856</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3544</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2049; 6101</t>
+          <t>2410; 6103</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1399; 6395</t>
+          <t>744; 5984</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3385; 7572</t>
+          <t>4046; 7572</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1355; 5760</t>
+          <t>1360; 5756</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>672; 4721</t>
+          <t>787; 4666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,27 +2859,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1046; 5378</t>
+          <t>1089; 5430</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>738; 4246</t>
+          <t>707; 4221</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4015; 9522</t>
+          <t>4092; 9534</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3510; 9744</t>
+          <t>3834; 10081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2849; 8093</t>
+          <t>2980; 8339</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>580; 3788</t>
+          <t>596; 4046</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>633; 4439</t>
+          <t>665; 4878</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1949; 7224</t>
+          <t>1767; 7358</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2055; 7561</t>
+          <t>1827; 7138</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1856; 6859</t>
+          <t>1726; 6680</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1496; 6260</t>
+          <t>1699; 6369</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3064; 9624</t>
+          <t>3225; 9653</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3723; 9917</t>
+          <t>3551; 9915</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4889; 12055</t>
+          <t>4674; 12118</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19310; 29995</t>
+          <t>19323; 29890</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25338; 37976</t>
+          <t>25203; 38201</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20062; 32430</t>
+          <t>20027; 31390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16241; 26946</t>
+          <t>15846; 27115</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23341; 36335</t>
+          <t>22908; 36394</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16019; 27576</t>
+          <t>16210; 27319</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38578; 53788</t>
+          <t>39041; 54428</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>52194; 70015</t>
+          <t>52614; 70406</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39679; 55447</t>
+          <t>39078; 55388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>55,31%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>66,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>44,91%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>62,84%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,7; 88,55</t>
+          <t>34,28; 89,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,37; 100,0</t>
+          <t>0,0; 67,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,91; 74,27</t>
+          <t>18,7; 70,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,55; 91,1</t>
+          <t>21,41; 81,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,24; 63,96</t>
+          <t>22,7; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,39; 70,37</t>
+          <t>18,78; 72,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,72; 80,04</t>
+          <t>37,54; 80,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,28; 68,53</t>
+          <t>21,81; 69,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 62,72</t>
+          <t>24,89; 63,6</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50,63%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>57,09%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>45,62%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>83,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>44,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,26%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>50,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,71; 77,5</t>
+          <t>11,35; 76,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,31; 69,68</t>
+          <t>42,42; 83,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,62; 100,0</t>
+          <t>24,37; 75,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 77,55</t>
+          <t>32,79; 80,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,23; 82,57</t>
+          <t>22,17; 68,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,44; 76,61</t>
+          <t>51,4; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 71,18</t>
+          <t>34,21; 72,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,96; 70,34</t>
+          <t>40,5; 70,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,51; 84,54</t>
+          <t>48,55; 82,85</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50,56%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>74,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>52,55%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>79,78%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>57,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,67; 100,0</t>
+          <t>20,13; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,45; 80,96</t>
+          <t>18,88; 86,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,26; 80,46</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19,89; 100,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>26,74; 86,68</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,02; 100,0</t>
+          <t>41,91; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,27; 75,58</t>
+          <t>35,13; 75,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 100,0</t>
+          <t>21,31; 100,0</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42,16%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>24,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>44,66%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>31,33%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,15</t>
+          <t>17,17; 75,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 72,26</t>
+          <t>10,67; 79,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 61,19</t>
+          <t>19,28; 76,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,14; 74,66</t>
+          <t>0,0; 62,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 78,94</t>
+          <t>17,9; 71,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 73,69</t>
+          <t>11,4; 61,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 57,14</t>
+          <t>16,17; 58,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 66,47</t>
+          <t>22,43; 64,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,21; 61,99</t>
+          <t>23,63; 59,99</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>83,69%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>33,44%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,3; 100,0</t>
+          <t>11,38; 79,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,58</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 80,13</t>
+          <t>49,5; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 76,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,52; 85,55</t>
+          <t>42,7; 86,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 68,44</t>
+          <t>9,53; 66,38</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>78,63%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27,78%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>62,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>30,58%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78,63%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>27,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,42 +1228,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,29; 100,0</t>
+          <t>20,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,84</t>
+          <t>0,0; 71,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20,24; 100,0</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 74,31</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>18,89; 100,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 71,06</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,74; 90,49</t>
+          <t>37,68; 90,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 58,34</t>
+          <t>7,27; 58,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16,05%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58,33%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>81,53%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>48,99%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>45,06%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,43; 100,0</t>
+          <t>0,0; 65,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,01; 80,41</t>
+          <t>17,76; 89,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,22; 78,4</t>
+          <t>14,92; 87,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,39</t>
+          <t>45,12; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 89,89</t>
+          <t>18,52; 78,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,59; 87,09</t>
+          <t>11,81; 78,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,23; 82,08</t>
+          <t>34,44; 81,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 76,39</t>
+          <t>28,83; 74,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27,59; 77,23</t>
+          <t>25,23; 76,69</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>31,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35,93%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>32,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>35,65%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>32,08%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>35,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,28; 69,72</t>
+          <t>14,38; 55,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,67; 70,89</t>
+          <t>18,17; 66,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,03; 54,26</t>
+          <t>16,39; 62,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,15; 51,38</t>
+          <t>10,14; 71,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,67; 64,53</t>
+          <t>8,82; 64,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,53; 61,95</t>
+          <t>15,71; 57,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,37; 49,01</t>
+          <t>16,83; 50,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,6; 57,53</t>
+          <t>18,95; 56,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,61; 50,83</t>
+          <t>19,22; 50,27</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>55,95%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>51,24%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>46,35%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44,04; 68,12</t>
+          <t>35,85; 58,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41,12; 62,33</t>
+          <t>38,07; 58,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36,33; 56,94</t>
+          <t>33,32; 57,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,93; 58,05</t>
+          <t>43,51; 67,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,04; 57,26</t>
+          <t>41,82; 62,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,87; 57,08</t>
+          <t>35,69; 57,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,1; 60,09</t>
+          <t>42,54; 58,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,14; 56,39</t>
+          <t>41,96; 56,64</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,95; 53,78</t>
+          <t>38,2; 53,8</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,27 +1755,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4959</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3168</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3264</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4117</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4959</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2478</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4280</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1243; 5071</t>
+          <t>2705; 7089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1254; 4945</t>
+          <t>0; 5551</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1826; 6808</t>
+          <t>1895; 7180</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2253; 7190</t>
+          <t>1226; 4678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>678; 5262</t>
+          <t>1123; 4945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1560; 7133</t>
+          <t>1721; 6607</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4865; 10901</t>
+          <t>5113; 10960</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2935; 9027</t>
+          <t>2873; 9129</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4700; 12107</t>
+          <t>4804; 12277</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5884</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5538</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7659</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8936</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4054</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3062; 7989</t>
+          <t>660; 4476</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2830; 8458</t>
+          <t>5899; 11563</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4756; 9215</t>
+          <t>1952; 6084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>661; 4514</t>
+          <t>3380; 8347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6011; 11482</t>
+          <t>2692; 8348</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2037; 6134</t>
+          <t>4737; 9215</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5327; 11479</t>
+          <t>5517; 11623</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10406; 18319</t>
+          <t>10547; 18400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8354; 14560</t>
+          <t>8362; 14268</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4209</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2245</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4215</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2149</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4209</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>715; 3022</t>
+          <t>632; 3138</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2042; 6494</t>
+          <t>1374; 6290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 1355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3022</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1706; 6455</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>624; 3138</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1946; 6310</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1355</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2588; 6160</t>
+          <t>2582; 6160</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4939; 11565</t>
+          <t>5376; 11506</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>741; 3504</t>
+          <t>747; 3504</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2678</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4720</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1587</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3812</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3083</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2678</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4720</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>1403; 6192</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1631; 6169</t>
+          <t>678; 5045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1091; 6022</t>
+          <t>1866; 7369</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1401; 6101</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>672; 5015</t>
+          <t>1528; 6125</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1872; 7135</t>
+          <t>1122; 6044</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2409; 8355</t>
+          <t>2365; 8619</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3253; 9896</t>
+          <t>3340; 9667</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4532; 12103</t>
+          <t>4614; 11712</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>7021</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1508</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2897</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4723; 8390</t>
+          <t>724; 5063</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3455</t>
+          <t>0; 1784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>724; 5103</t>
+          <t>4153; 8390</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1784</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6276; 12626</t>
+          <t>6303; 12747</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>595; 4308</t>
+          <t>600; 4179</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2295</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1597</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,42 +2676,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>743; 3662</t>
+          <t>616; 3082</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3856</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0; 1766</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>741; 3662</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3881</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>582; 3082</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3578</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 1766</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2410; 6103</t>
+          <t>2541; 6112</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>744; 5984</t>
+          <t>745; 5991</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,27 +2733,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>6173</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3507</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2681</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2827</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4046; 7572</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1360; 5756</t>
+          <t>1073; 5400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>787; 4666</t>
+          <t>723; 4246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>3416; 7572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1089; 5430</t>
+          <t>1326; 5602</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>707; 4221</t>
+          <t>703; 4667</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4092; 9534</t>
+          <t>4000; 9491</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3834; 10081</t>
+          <t>3805; 9885</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2980; 8339</t>
+          <t>2724; 8281</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4411</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3971</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1865</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2453</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4351</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4411</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3971</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3693</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>596; 4046</t>
+          <t>1998; 7661</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>665; 4878</t>
+          <t>1881; 6864</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1767; 7358</t>
+          <t>1685; 6414</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1827; 7138</t>
+          <t>589; 4148</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1726; 6680</t>
+          <t>607; 4462</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1699; 6369</t>
+          <t>2131; 7860</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3225; 9653</t>
+          <t>3316; 9984</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3551; 9915</t>
+          <t>3265; 9789</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4674; 12118</t>
+          <t>4583; 11985</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>24550</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>31407</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>25548</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>29929</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>21805</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19323; 29890</t>
+          <t>16742; 27521</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25203; 38201</t>
+          <t>24197; 37194</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20027; 31390</t>
+          <t>15946; 27450</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15846; 27115</t>
+          <t>19092; 29770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>22908; 36394</t>
+          <t>25632; 38324</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16210; 27319</t>
+          <t>19674; 31540</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39041; 54428</t>
+          <t>38531; 53426</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>52614; 70406</t>
+          <t>52393; 70713</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39078; 55388</t>
+          <t>39342; 55408</t>
         </is>
       </c>
     </row>
